--- a/Experiments/outputs/scenario_7_np.xlsx
+++ b/Experiments/outputs/scenario_7_np.xlsx
@@ -530,55 +530,55 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>186.3737762721394</v>
+        <v>236.2763896879593</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08202195167541504</v>
+        <v>0.1174190044403076</v>
       </c>
       <c r="E2" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H2" t="n">
-        <v>384.1269603715025</v>
+        <v>460.6888467527651</v>
       </c>
       <c r="I2" t="n">
-        <v>0.168349027633667</v>
+        <v>0.2944021224975586</v>
       </c>
       <c r="J2" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L2" t="n">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="M2" t="n">
-        <v>1261.80003780524</v>
+        <v>1360.964669802402</v>
       </c>
       <c r="N2" t="n">
-        <v>2.338376760482788</v>
+        <v>1.686746120452881</v>
       </c>
       <c r="O2" t="n">
-        <v>392</v>
+        <v>317</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>1040</v>
+        <v>893</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8522953156695765</v>
+        <v>0.8263905045218666</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6955722389740546</v>
+        <v>0.6614983055955065</v>
       </c>
     </row>
     <row r="3">
@@ -591,55 +591,55 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>182.5449299317585</v>
+        <v>224.1371551493089</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07032895088195801</v>
+        <v>0.1537380218505859</v>
       </c>
       <c r="E3" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="F3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" t="n">
         <v>8</v>
       </c>
-      <c r="G3" t="n">
-        <v>6</v>
-      </c>
       <c r="H3" t="n">
-        <v>540.5412808693118</v>
+        <v>442.9873959519416</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2580065727233887</v>
+        <v>0.4003598690032959</v>
       </c>
       <c r="J3" t="n">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="K3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L3" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="M3" t="n">
-        <v>1348.672867213744</v>
+        <v>1385.665866561628</v>
       </c>
       <c r="N3" t="n">
-        <v>2.817896842956543</v>
+        <v>1.388882875442505</v>
       </c>
       <c r="O3" t="n">
-        <v>389</v>
+        <v>342</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8646484745341673</v>
+        <v>0.838245885564404</v>
       </c>
       <c r="S3" t="n">
-        <v>0.599205045189328</v>
+        <v>0.6803072034593994</v>
       </c>
     </row>
     <row r="4">
@@ -652,55 +652,55 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>184.8693787909573</v>
+        <v>278.0792231499614</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1422581672668457</v>
+        <v>0.09191703796386719</v>
       </c>
       <c r="E4" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G4" t="n">
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>426.959095111871</v>
+        <v>536.5340314562272</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4918088912963867</v>
+        <v>0.4156370162963867</v>
       </c>
       <c r="J4" t="n">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L4" t="n">
-        <v>98</v>
+        <v>158</v>
       </c>
       <c r="M4" t="n">
-        <v>1287.931961016735</v>
+        <v>1359.813753221213</v>
       </c>
       <c r="N4" t="n">
-        <v>2.719092845916748</v>
+        <v>1.979492664337158</v>
       </c>
       <c r="O4" t="n">
-        <v>404</v>
+        <v>348</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1069</v>
+        <v>946</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8564602910816692</v>
+        <v>0.7955019777589174</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6684925073411365</v>
+        <v>0.6054356486796435</v>
       </c>
     </row>
     <row r="5">
@@ -713,55 +713,55 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>213.4908684172946</v>
+        <v>243.4858009463155</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1220102310180664</v>
+        <v>0.1882810592651367</v>
       </c>
       <c r="E5" t="n">
         <v>65</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>436.9743229141756</v>
+        <v>514.4174270107108</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4404470920562744</v>
+        <v>0.6367008686065674</v>
       </c>
       <c r="J5" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="K5" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L5" t="n">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="M5" t="n">
-        <v>1316.960572017359</v>
+        <v>1441.929416402581</v>
       </c>
       <c r="N5" t="n">
-        <v>3.120663166046143</v>
+        <v>1.979923963546753</v>
       </c>
       <c r="O5" t="n">
-        <v>382</v>
+        <v>350</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1064</v>
+        <v>965</v>
       </c>
       <c r="R5" t="n">
-        <v>0.837891222445435</v>
+        <v>0.8311388905888475</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6681948327087686</v>
+        <v>0.6432436836651044</v>
       </c>
     </row>
     <row r="6">
@@ -774,55 +774,55 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>203.350529170962</v>
+        <v>219.3560404396771</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2529220581054688</v>
+        <v>0.2122900485992432</v>
       </c>
       <c r="E6" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H6" t="n">
-        <v>476.5444961059758</v>
+        <v>511.636513144359</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7949981689453125</v>
+        <v>0.5801479816436768</v>
       </c>
       <c r="J6" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="K6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L6" t="n">
-        <v>115</v>
+        <v>150</v>
       </c>
       <c r="M6" t="n">
-        <v>1316.114273423354</v>
+        <v>1337.886665214623</v>
       </c>
       <c r="N6" t="n">
-        <v>1.900699138641357</v>
+        <v>2.726936817169189</v>
       </c>
       <c r="O6" t="n">
-        <v>390</v>
+        <v>339</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1044</v>
+        <v>933</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8454917378549316</v>
+        <v>0.836042883046085</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6379155627068518</v>
+        <v>0.6175785838613745</v>
       </c>
     </row>
     <row r="7">
@@ -835,55 +835,55 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>227.0143354715585</v>
+        <v>207.6544789376589</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07205295562744141</v>
+        <v>0.1715941429138184</v>
       </c>
       <c r="E7" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F7" t="n">
         <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H7" t="n">
-        <v>450.4824365487522</v>
+        <v>510.3343667760438</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2563440799713135</v>
+        <v>0.4550197124481201</v>
       </c>
       <c r="J7" t="n">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="K7" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L7" t="n">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="M7" t="n">
-        <v>1300.124334240277</v>
+        <v>1308.444074281168</v>
       </c>
       <c r="N7" t="n">
-        <v>3.015799999237061</v>
+        <v>1.378446102142334</v>
       </c>
       <c r="O7" t="n">
-        <v>376</v>
+        <v>334</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1008</v>
+        <v>946</v>
       </c>
       <c r="R7" t="n">
-        <v>0.8253902880725531</v>
+        <v>0.8412966339033329</v>
       </c>
       <c r="S7" t="n">
-        <v>0.653508187882669</v>
+        <v>0.6099685291811874</v>
       </c>
     </row>
     <row r="8">
@@ -896,55 +896,55 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>209.1244264500497</v>
+        <v>237.432998958207</v>
       </c>
       <c r="D8" t="n">
-        <v>0.392099142074585</v>
+        <v>0.1034688949584961</v>
       </c>
       <c r="E8" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H8" t="n">
-        <v>438.1680477951279</v>
+        <v>493.0845507009567</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2336831092834473</v>
+        <v>0.3236916065216064</v>
       </c>
       <c r="J8" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="K8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L8" t="n">
-        <v>88</v>
+        <v>138</v>
       </c>
       <c r="M8" t="n">
-        <v>1344.255151503378</v>
+        <v>1330.626581697254</v>
       </c>
       <c r="N8" t="n">
-        <v>1.638968944549561</v>
+        <v>1.546625137329102</v>
       </c>
       <c r="O8" t="n">
-        <v>383</v>
+        <v>350</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>996</v>
+        <v>955</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8444310023910485</v>
+        <v>0.8215630123251002</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6740439883714837</v>
+        <v>0.6294343150187091</v>
       </c>
     </row>
     <row r="9">
@@ -957,55 +957,55 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>213.671970500475</v>
+        <v>219.5247636459092</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1184778213500977</v>
+        <v>0.1292569637298584</v>
       </c>
       <c r="E9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H9" t="n">
-        <v>452.5559122336102</v>
+        <v>553.3211847492767</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2598800659179688</v>
+        <v>0.5416040420532227</v>
       </c>
       <c r="J9" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="K9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
-        <v>99</v>
+        <v>160</v>
       </c>
       <c r="M9" t="n">
-        <v>1339.636116042244</v>
+        <v>1482.699630699215</v>
       </c>
       <c r="N9" t="n">
-        <v>1.604164838790894</v>
+        <v>1.667432308197021</v>
       </c>
       <c r="O9" t="n">
-        <v>405</v>
+        <v>352</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1054</v>
+        <v>987</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8404999925414544</v>
+        <v>0.8519425249048014</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6621799705052598</v>
+        <v>0.6268150518872523</v>
       </c>
     </row>
     <row r="10">
@@ -1018,55 +1018,55 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>243.9816949262223</v>
+        <v>169.0774972306189</v>
       </c>
       <c r="D10" t="n">
-        <v>0.08269000053405762</v>
+        <v>0.1100049018859863</v>
       </c>
       <c r="E10" t="n">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="F10" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H10" t="n">
-        <v>492.2251966443483</v>
+        <v>526.453709830566</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2815690040588379</v>
+        <v>0.4663200378417969</v>
       </c>
       <c r="J10" t="n">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L10" t="n">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="M10" t="n">
-        <v>1299.330818953016</v>
+        <v>1366.65690484926</v>
       </c>
       <c r="N10" t="n">
-        <v>1.614214897155762</v>
+        <v>1.321554183959961</v>
       </c>
       <c r="O10" t="n">
-        <v>404</v>
+        <v>322</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1052</v>
+        <v>889</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8122251151382526</v>
+        <v>0.876283874445234</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6211702289637236</v>
+        <v>0.6147872169214021</v>
       </c>
     </row>
     <row r="11">
@@ -1079,55 +1079,55 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>199.8044638053541</v>
+        <v>227.3009273906201</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1031868457794189</v>
+        <v>0.09553813934326172</v>
       </c>
       <c r="E11" t="n">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H11" t="n">
-        <v>440.472515866202</v>
+        <v>471.0749634945568</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2949240207672119</v>
+        <v>0.3554480075836182</v>
       </c>
       <c r="J11" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="K11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L11" t="n">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="M11" t="n">
-        <v>1322.585721284146</v>
+        <v>1407.741111877224</v>
       </c>
       <c r="N11" t="n">
-        <v>1.767919778823853</v>
+        <v>1.35706901550293</v>
       </c>
       <c r="O11" t="n">
-        <v>402</v>
+        <v>372</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1018</v>
+        <v>1027</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8489289120622315</v>
+        <v>0.8385349937762959</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6669610832948268</v>
+        <v>0.6653681848742927</v>
       </c>
     </row>
     <row r="12">
@@ -1140,55 +1140,55 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>205.5071700485397</v>
+        <v>273.4556571758453</v>
       </c>
       <c r="D12" t="n">
-        <v>0.07362508773803711</v>
+        <v>0.0850980281829834</v>
       </c>
       <c r="E12" t="n">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H12" t="n">
-        <v>417.5306440132707</v>
+        <v>445.3827106724122</v>
       </c>
       <c r="I12" t="n">
-        <v>0.288801908493042</v>
+        <v>0.3422448635101318</v>
       </c>
       <c r="J12" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="K12" t="n">
         <v>8</v>
       </c>
       <c r="L12" t="n">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="M12" t="n">
-        <v>1331.441980813547</v>
+        <v>1330.49514283232</v>
       </c>
       <c r="N12" t="n">
-        <v>1.490791797637939</v>
+        <v>1.561079025268555</v>
       </c>
       <c r="O12" t="n">
-        <v>407</v>
+        <v>325</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>1100</v>
+        <v>864</v>
       </c>
       <c r="R12" t="n">
-        <v>0.8456506757260507</v>
+        <v>0.7944707587629964</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6864071810638358</v>
+        <v>0.6652504046543948</v>
       </c>
     </row>
     <row r="13">
@@ -1201,55 +1201,55 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>184.3193169271638</v>
+        <v>241.6815901327195</v>
       </c>
       <c r="D13" t="n">
-        <v>0.06574892997741699</v>
+        <v>0.1198148727416992</v>
       </c>
       <c r="E13" t="n">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H13" t="n">
-        <v>447.633519406231</v>
+        <v>508.6509315210412</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1874918937683105</v>
+        <v>0.4216492176055908</v>
       </c>
       <c r="J13" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="L13" t="n">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="M13" t="n">
-        <v>1320.304952268747</v>
+        <v>1352.173599516781</v>
       </c>
       <c r="N13" t="n">
-        <v>1.378254890441895</v>
+        <v>1.464825868606567</v>
       </c>
       <c r="O13" t="n">
-        <v>392</v>
+        <v>343</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1048</v>
+        <v>924</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8603964056860965</v>
+        <v>0.8212643774297265</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6609620234802273</v>
+        <v>0.6238271981476231</v>
       </c>
     </row>
     <row r="14">
@@ -1262,55 +1262,55 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>181.0253282009136</v>
+        <v>198.5055104205379</v>
       </c>
       <c r="D14" t="n">
-        <v>0.05892825126647949</v>
+        <v>0.1392817497253418</v>
       </c>
       <c r="E14" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H14" t="n">
-        <v>411.4260911353785</v>
+        <v>540.8729140922442</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1515078544616699</v>
+        <v>0.4419267177581787</v>
       </c>
       <c r="J14" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L14" t="n">
-        <v>93</v>
+        <v>152</v>
       </c>
       <c r="M14" t="n">
-        <v>1307.448099131619</v>
+        <v>1354.088910539772</v>
       </c>
       <c r="N14" t="n">
-        <v>1.328319787979126</v>
+        <v>1.382253170013428</v>
       </c>
       <c r="O14" t="n">
-        <v>385</v>
+        <v>328</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1028</v>
+        <v>921</v>
       </c>
       <c r="R14" t="n">
-        <v>0.8615430101423168</v>
+        <v>0.8534028977894746</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6853212824213522</v>
+        <v>0.6005632201236776</v>
       </c>
     </row>
     <row r="15">
@@ -1323,55 +1323,55 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>217.3212655079982</v>
+        <v>228.2342169811405</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1396021842956543</v>
+        <v>0.08927702903747559</v>
       </c>
       <c r="E15" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="F15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H15" t="n">
-        <v>418.4190692769344</v>
+        <v>579.0933377308938</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3220551013946533</v>
+        <v>0.3632960319519043</v>
       </c>
       <c r="J15" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K15" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="L15" t="n">
-        <v>101</v>
+        <v>150</v>
       </c>
       <c r="M15" t="n">
-        <v>1331.141335764218</v>
+        <v>1338.860633924239</v>
       </c>
       <c r="N15" t="n">
-        <v>1.687582015991211</v>
+        <v>1.432238101959229</v>
       </c>
       <c r="O15" t="n">
-        <v>414</v>
+        <v>345</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1084</v>
+        <v>932</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8367406527998529</v>
+        <v>0.829531012266617</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6856689383500237</v>
+        <v>0.5674730266483714</v>
       </c>
     </row>
     <row r="16">
@@ -1384,55 +1384,55 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>188.3555531117894</v>
+        <v>221.4193114856069</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0825958251953125</v>
+        <v>0.1071538925170898</v>
       </c>
       <c r="E16" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>436.820567310106</v>
+        <v>497.3821040891837</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2053909301757812</v>
+        <v>0.3046910762786865</v>
       </c>
       <c r="J16" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="K16" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="L16" t="n">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="M16" t="n">
-        <v>1291.620135235368</v>
+        <v>1418.535833066945</v>
       </c>
       <c r="N16" t="n">
-        <v>1.766300201416016</v>
+        <v>1.76378607749939</v>
       </c>
       <c r="O16" t="n">
-        <v>391</v>
+        <v>351</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1051</v>
+        <v>993</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8541710925887155</v>
+        <v>0.8439099624245041</v>
       </c>
       <c r="S16" t="n">
-        <v>0.661804151705559</v>
+        <v>0.6493693761589238</v>
       </c>
     </row>
     <row r="17">
@@ -1445,55 +1445,55 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>193.7923647250601</v>
+        <v>271.4879762762066</v>
       </c>
       <c r="D17" t="n">
-        <v>0.06732797622680664</v>
+        <v>0.1374828815460205</v>
       </c>
       <c r="E17" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="F17" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>482.7506524891348</v>
+        <v>572.1799417660467</v>
       </c>
       <c r="I17" t="n">
-        <v>0.227679967880249</v>
+        <v>0.6422240734100342</v>
       </c>
       <c r="J17" t="n">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="K17" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L17" t="n">
-        <v>121</v>
+        <v>163</v>
       </c>
       <c r="M17" t="n">
-        <v>1295.291921364374</v>
+        <v>1389.456980666266</v>
       </c>
       <c r="N17" t="n">
-        <v>1.541290998458862</v>
+        <v>1.689574956893921</v>
       </c>
       <c r="O17" t="n">
-        <v>382</v>
+        <v>353</v>
       </c>
       <c r="P17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1029</v>
+        <v>994</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8503871123345444</v>
+        <v>0.8046085772687803</v>
       </c>
       <c r="S17" t="n">
-        <v>0.627303587302052</v>
+        <v>0.5881988793264563</v>
       </c>
     </row>
     <row r="18">
@@ -1506,55 +1506,55 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>233.8862737986371</v>
+        <v>202.0459655095287</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1202270984649658</v>
+        <v>0.1006519794464111</v>
       </c>
       <c r="E18" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>500.5421363614528</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.4242730140686035</v>
+      </c>
+      <c r="J18" t="n">
+        <v>94</v>
+      </c>
+      <c r="K18" t="n">
         <v>10</v>
       </c>
-      <c r="H18" t="n">
-        <v>513.8728428981793</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.321707010269165</v>
-      </c>
-      <c r="J18" t="n">
-        <v>106</v>
-      </c>
-      <c r="K18" t="n">
-        <v>11</v>
-      </c>
       <c r="L18" t="n">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="M18" t="n">
-        <v>1329.345619012298</v>
+        <v>1355.426617345563</v>
       </c>
       <c r="N18" t="n">
-        <v>1.701043128967285</v>
+        <v>1.54892897605896</v>
       </c>
       <c r="O18" t="n">
-        <v>398</v>
+        <v>338</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1083</v>
+        <v>944</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8240590930954327</v>
+        <v>0.8509355188071995</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6134392474396642</v>
+        <v>0.6307124783031756</v>
       </c>
     </row>
     <row r="19">
@@ -1567,55 +1567,55 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>177.471249443255</v>
+        <v>206.1816773185753</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1714391708374023</v>
+        <v>0.1142458915710449</v>
       </c>
       <c r="E19" t="n">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H19" t="n">
-        <v>423.7380666002262</v>
+        <v>539.1629001743177</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3344628810882568</v>
+        <v>0.4529070854187012</v>
       </c>
       <c r="J19" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="K19" t="n">
         <v>11</v>
       </c>
       <c r="L19" t="n">
-        <v>104</v>
+        <v>165</v>
       </c>
       <c r="M19" t="n">
-        <v>1334.287440265548</v>
+        <v>1339.515985252297</v>
       </c>
       <c r="N19" t="n">
-        <v>2.379561901092529</v>
+        <v>1.405460119247437</v>
       </c>
       <c r="O19" t="n">
-        <v>400</v>
+        <v>345</v>
       </c>
       <c r="P19" t="n">
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>1069</v>
+        <v>958</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8669917409940282</v>
+        <v>0.8460774790382654</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6824237013608595</v>
+        <v>0.5974942396280799</v>
       </c>
     </row>
     <row r="20">
@@ -1628,55 +1628,55 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>208.888914639654</v>
+        <v>236.6217585877027</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1542680263519287</v>
+        <v>0.1132519245147705</v>
       </c>
       <c r="E20" t="n">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="F20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20" t="n">
-        <v>457.388356482246</v>
+        <v>482.2873217934077</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6095380783081055</v>
+        <v>0.3501079082489014</v>
       </c>
       <c r="J20" t="n">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="K20" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L20" t="n">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="M20" t="n">
-        <v>1303.071628825086</v>
+        <v>1326.372026619508</v>
       </c>
       <c r="N20" t="n">
-        <v>2.519912958145142</v>
+        <v>2.149223327636719</v>
       </c>
       <c r="O20" t="n">
-        <v>385</v>
+        <v>335</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1042</v>
+        <v>918</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8396949868151157</v>
+        <v>0.8216022700729185</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6489921610106344</v>
+        <v>0.6363860876781293</v>
       </c>
     </row>
     <row r="21">
@@ -1689,55 +1689,55 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>230.475592646947</v>
+        <v>186.2414729023476</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0899350643157959</v>
+        <v>0.09141802787780762</v>
       </c>
       <c r="E21" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F21" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>489.4025066978157</v>
+        <v>499.8406446516336</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3747718334197998</v>
+        <v>0.2940270900726318</v>
       </c>
       <c r="J21" t="n">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="K21" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L21" t="n">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="M21" t="n">
-        <v>1317.485694732944</v>
+        <v>1323.710312562965</v>
       </c>
       <c r="N21" t="n">
-        <v>2.133158206939697</v>
+        <v>1.570259094238281</v>
       </c>
       <c r="O21" t="n">
-        <v>383</v>
+        <v>327</v>
       </c>
       <c r="P21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1064</v>
+        <v>931</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8250640644005893</v>
+        <v>0.8593034509629623</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6285329634664319</v>
+        <v>0.6223942354246351</v>
       </c>
     </row>
     <row r="22">
@@ -1750,55 +1750,55 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>250.7560077042097</v>
+        <v>235.6705458927451</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1165850162506104</v>
+        <v>0.1116032600402832</v>
       </c>
       <c r="E22" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G22" t="n">
         <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>428.7222568011678</v>
+        <v>503.3901159888443</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3574800491333008</v>
+        <v>0.4107358455657959</v>
       </c>
       <c r="J22" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="K22" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L22" t="n">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="M22" t="n">
-        <v>1319.245242705844</v>
+        <v>1445.425836758129</v>
       </c>
       <c r="N22" t="n">
-        <v>2.860442876815796</v>
+        <v>2.615444898605347</v>
       </c>
       <c r="O22" t="n">
-        <v>396</v>
+        <v>345</v>
       </c>
       <c r="P22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q22" t="n">
-        <v>1030</v>
+        <v>979</v>
       </c>
       <c r="R22" t="n">
-        <v>0.8099246451024561</v>
+        <v>0.836954245662774</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6750245951830495</v>
+        <v>0.6517357700496955</v>
       </c>
     </row>
     <row r="23">
@@ -1811,13 +1811,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>225.1234463821085</v>
+        <v>221.4093091174934</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1220879554748535</v>
+        <v>0.2003591060638428</v>
       </c>
       <c r="E23" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="F23" t="n">
         <v>11</v>
@@ -1826,40 +1826,40 @@
         <v>4</v>
       </c>
       <c r="H23" t="n">
-        <v>463.6238841176781</v>
+        <v>435.0312526774106</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3220810890197754</v>
+        <v>0.3325109481811523</v>
       </c>
       <c r="J23" t="n">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="K23" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="L23" t="n">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="M23" t="n">
-        <v>1280.900032789721</v>
+        <v>1409.297210057187</v>
       </c>
       <c r="N23" t="n">
-        <v>3.197780132293701</v>
+        <v>1.436139106750488</v>
       </c>
       <c r="O23" t="n">
-        <v>381</v>
+        <v>338</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>960</v>
+        <v>936</v>
       </c>
       <c r="R23" t="n">
-        <v>0.824245889125474</v>
+        <v>0.8428938143512616</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6380483470611411</v>
+        <v>0.691313337191835</v>
       </c>
     </row>
     <row r="24">
@@ -1872,55 +1872,55 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>253.578566113545</v>
+        <v>247.3803967875503</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1239922046661377</v>
+        <v>0.08690595626831055</v>
       </c>
       <c r="E24" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="F24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G24" t="n">
         <v>5</v>
       </c>
       <c r="H24" t="n">
-        <v>426.5970061892455</v>
+        <v>506.285770260203</v>
       </c>
       <c r="I24" t="n">
-        <v>0.378791332244873</v>
+        <v>0.348599910736084</v>
       </c>
       <c r="J24" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L24" t="n">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="M24" t="n">
-        <v>1282.163709659078</v>
+        <v>1327.566466301889</v>
       </c>
       <c r="N24" t="n">
-        <v>1.555621147155762</v>
+        <v>1.630389928817749</v>
       </c>
       <c r="O24" t="n">
-        <v>394</v>
+        <v>308</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1062</v>
+        <v>845</v>
       </c>
       <c r="R24" t="n">
-        <v>0.8022260619270136</v>
+        <v>0.813658748494408</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6672835122570459</v>
+        <v>0.6186362166328828</v>
       </c>
     </row>
     <row r="25">
@@ -1933,55 +1933,55 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>225.716039739842</v>
+        <v>269.8599553281367</v>
       </c>
       <c r="D25" t="n">
-        <v>0.07732129096984863</v>
+        <v>0.8622751235961914</v>
       </c>
       <c r="E25" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G25" t="n">
         <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>449.6378397440421</v>
+        <v>479.3241141213728</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2412240505218506</v>
+        <v>0.9350960254669189</v>
       </c>
       <c r="J25" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="K25" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L25" t="n">
-        <v>91</v>
+        <v>142</v>
       </c>
       <c r="M25" t="n">
-        <v>1344.56150200461</v>
+        <v>1400.926871961234</v>
       </c>
       <c r="N25" t="n">
-        <v>1.673365831375122</v>
+        <v>2.135138034820557</v>
       </c>
       <c r="O25" t="n">
-        <v>400</v>
+        <v>326</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1075</v>
+        <v>879</v>
       </c>
       <c r="R25" t="n">
-        <v>0.8321266528877098</v>
+        <v>0.8073704197347967</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6655877480697788</v>
+        <v>0.6578521522323711</v>
       </c>
     </row>
     <row r="26">
@@ -1994,55 +1994,55 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>224.4466482482796</v>
+        <v>213.6302794181343</v>
       </c>
       <c r="D26" t="n">
-        <v>0.06398582458496094</v>
+        <v>0.1187636852264404</v>
       </c>
       <c r="E26" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G26" t="n">
         <v>5</v>
       </c>
       <c r="H26" t="n">
-        <v>420.5719671752025</v>
+        <v>477.3331803162916</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3556962013244629</v>
+        <v>0.3671441078186035</v>
       </c>
       <c r="J26" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K26" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="L26" t="n">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="M26" t="n">
-        <v>1283.890039503557</v>
+        <v>1372.374381946766</v>
       </c>
       <c r="N26" t="n">
-        <v>2.311903953552246</v>
+        <v>2.168518781661987</v>
       </c>
       <c r="O26" t="n">
-        <v>401</v>
+        <v>339</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>1092</v>
+        <v>931</v>
       </c>
       <c r="R26" t="n">
-        <v>0.8251823432362894</v>
+        <v>0.8443352759798012</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6724236856469223</v>
+        <v>0.6521844282467761</v>
       </c>
     </row>
     <row r="27">
@@ -2055,55 +2055,55 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>206.2288834165793</v>
+        <v>207.1038935856386</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1192326545715332</v>
+        <v>0.2223141193389893</v>
       </c>
       <c r="E27" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F27" t="n">
+        <v>9</v>
+      </c>
+      <c r="G27" t="n">
         <v>8</v>
       </c>
-      <c r="G27" t="n">
-        <v>12</v>
-      </c>
       <c r="H27" t="n">
-        <v>446.034886181598</v>
+        <v>544.7854488029003</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4340841770172119</v>
+        <v>0.6178021430969238</v>
       </c>
       <c r="J27" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="K27" t="n">
         <v>11</v>
       </c>
       <c r="L27" t="n">
-        <v>106</v>
+        <v>162</v>
       </c>
       <c r="M27" t="n">
-        <v>1357.576541024118</v>
+        <v>1352.625595739655</v>
       </c>
       <c r="N27" t="n">
-        <v>2.221864938735962</v>
+        <v>1.82916522026062</v>
       </c>
       <c r="O27" t="n">
-        <v>400</v>
+        <v>336</v>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1088</v>
+        <v>887</v>
       </c>
       <c r="R27" t="n">
-        <v>0.8480904190779505</v>
+        <v>0.8468874947820367</v>
       </c>
       <c r="S27" t="n">
-        <v>0.6714477064806071</v>
+        <v>0.5972385481105763</v>
       </c>
     </row>
     <row r="28">
@@ -2116,55 +2116,55 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>196.0710314254342</v>
+        <v>271.6133447956784</v>
       </c>
       <c r="D28" t="n">
-        <v>0.457089900970459</v>
+        <v>0.1517128944396973</v>
       </c>
       <c r="E28" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="F28" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G28" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>430.6624920818981</v>
+        <v>535.1896148078388</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8434658050537109</v>
+        <v>0.4980490207672119</v>
       </c>
       <c r="J28" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="K28" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L28" t="n">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="M28" t="n">
-        <v>1305.020822718043</v>
+        <v>1390.99841687242</v>
       </c>
       <c r="N28" t="n">
-        <v>1.865117788314819</v>
+        <v>1.939681768417358</v>
       </c>
       <c r="O28" t="n">
-        <v>393</v>
+        <v>330</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1026</v>
+        <v>857</v>
       </c>
       <c r="R28" t="n">
-        <v>0.8497563962105481</v>
+        <v>0.8047349720164417</v>
       </c>
       <c r="S28" t="n">
-        <v>0.6699956931070785</v>
+        <v>0.6152478620276349</v>
       </c>
     </row>
     <row r="29">
@@ -2177,55 +2177,55 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>244.8163386753812</v>
+        <v>184.9903596173831</v>
       </c>
       <c r="D29" t="n">
-        <v>0.08215498924255371</v>
+        <v>0.1989822387695312</v>
       </c>
       <c r="E29" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F29" t="n">
+        <v>9</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>511.4793749266619</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.7050609588623047</v>
+      </c>
+      <c r="J29" t="n">
+        <v>98</v>
+      </c>
+      <c r="K29" t="n">
         <v>10</v>
       </c>
-      <c r="G29" t="n">
-        <v>3</v>
-      </c>
-      <c r="H29" t="n">
-        <v>364.5505880831669</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.3246369361877441</v>
-      </c>
-      <c r="J29" t="n">
-        <v>89</v>
-      </c>
-      <c r="K29" t="n">
-        <v>7</v>
-      </c>
       <c r="L29" t="n">
-        <v>94</v>
+        <v>150</v>
       </c>
       <c r="M29" t="n">
-        <v>1304.132334170877</v>
+        <v>1312.84198064269</v>
       </c>
       <c r="N29" t="n">
-        <v>1.914651870727539</v>
+        <v>2.81701135635376</v>
       </c>
       <c r="O29" t="n">
-        <v>400</v>
+        <v>330</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1054</v>
+        <v>944</v>
       </c>
       <c r="R29" t="n">
-        <v>0.8122764597880882</v>
+        <v>0.8590916787054427</v>
       </c>
       <c r="S29" t="n">
-        <v>0.7204650337000227</v>
+        <v>0.6104029407436591</v>
       </c>
     </row>
     <row r="30">
@@ -2238,55 +2238,55 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>169.6856070604099</v>
+        <v>204.6242423158722</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1047728061676025</v>
+        <v>0.2122406959533691</v>
       </c>
       <c r="E30" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G30" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H30" t="n">
-        <v>427.0876567108842</v>
+        <v>581.2980670281679</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3303020000457764</v>
+        <v>0.717839241027832</v>
       </c>
       <c r="J30" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="K30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L30" t="n">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="M30" t="n">
-        <v>1370.672184907263</v>
+        <v>1377.241908075256</v>
       </c>
       <c r="N30" t="n">
-        <v>3.437770128250122</v>
+        <v>1.787339925765991</v>
       </c>
       <c r="O30" t="n">
-        <v>382</v>
+        <v>317</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1040</v>
+        <v>843</v>
       </c>
       <c r="R30" t="n">
-        <v>0.8762026333292154</v>
+        <v>0.851424618205351</v>
       </c>
       <c r="S30" t="n">
-        <v>0.6884100652120696</v>
+        <v>0.5779259521367948</v>
       </c>
     </row>
     <row r="31">
@@ -2299,55 +2299,55 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>227.909306290379</v>
+        <v>206.3358387621667</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1283731460571289</v>
+        <v>0.1311612129211426</v>
       </c>
       <c r="E31" t="n">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="F31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H31" t="n">
-        <v>453.5111262310644</v>
+        <v>529.2268230806505</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2996110916137695</v>
+        <v>0.5840260982513428</v>
       </c>
       <c r="J31" t="n">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="K31" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L31" t="n">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="M31" t="n">
-        <v>1308.389907624917</v>
+        <v>1334.644192848215</v>
       </c>
       <c r="N31" t="n">
-        <v>1.44080114364624</v>
+        <v>2.134262084960938</v>
       </c>
       <c r="O31" t="n">
-        <v>396</v>
+        <v>320</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1097</v>
+        <v>858</v>
       </c>
       <c r="R31" t="n">
-        <v>0.8258093363742799</v>
+        <v>0.8454001149760874</v>
       </c>
       <c r="S31" t="n">
-        <v>0.6533822803216892</v>
+        <v>0.6034697292982282</v>
       </c>
     </row>
   </sheetData>
